--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aci-con2\Documents\UiPath\AMP14_00_LiberarCalculoCoste\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aci-cns\Documents\UiPath\AMP06_00_InformeSeguimientoRepuestos\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1BF46CC-7800-4C79-A9DD-1FDC89055229}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEC08C2C-4489-4330-865F-62FE950C529E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="75">
   <si>
     <t>Name</t>
   </si>
@@ -221,39 +221,55 @@
     <t>InitialInpuPath</t>
   </si>
   <si>
-    <t>LCCoste_InitialInpuPath</t>
-  </si>
-  <si>
     <t>Ruta del insumo inicial incluido el nombre del archivo</t>
   </si>
   <si>
     <t>InputSheetName</t>
   </si>
   <si>
-    <t>LCCoste_InputSheetName</t>
-  </si>
-  <si>
     <t>Nombre de la hoja por procesar del insumo inicial</t>
   </si>
   <si>
-    <t>Valores para iterar para la variante de costo y control ttraspaso</t>
-  </si>
-  <si>
-    <t>LCCoste_VarianteCostoTraspaso</t>
-  </si>
-  <si>
-    <t>VarianteCostoTraspaso</t>
+    <t>ISR_SAPVariantes</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>Nombres de variantes en SAP</t>
+  </si>
+  <si>
+    <t>SAPVariantes</t>
+  </si>
+  <si>
+    <t>ISR_SAPDisposicion</t>
+  </si>
+  <si>
+    <t>SAPDisposicion</t>
+  </si>
+  <si>
+    <t>Nombres de disposicion en SAP</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -342,13 +358,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2841,7 +2858,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:Z984"/>
+  <dimension ref="A1:Z983"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="31.85546875" customWidth="1"/>
@@ -2960,45 +2977,58 @@
       <c r="A7" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="B7" s="10" t="s">
-        <v>64</v>
+      <c r="B7" s="11" t="s">
+        <v>68</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>67</v>
+        <v>65</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>69</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="B9" s="10" t="s">
-        <v>70</v>
+      <c r="B9" s="11" t="s">
+        <v>67</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D9" s="10" t="s">
-        <v>69</v>
+      <c r="D9" s="11" t="s">
+        <v>70</v>
       </c>
     </row>
-    <row r="10" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>74</v>
+      </c>
+    </row>
     <row r="11" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="12" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="13" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -3192,7 +3222,7 @@
     <row r="201" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="202" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="203" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="204" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -3972,7 +4002,6 @@
     <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape" r:id="rId1"/>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aci-cns\Documents\UiPath\AMP06_00_InformeSeguimientoRepuestos\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEC08C2C-4489-4330-865F-62FE950C529E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4D75E32-DB33-479D-93E4-D2F8217293B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="82">
   <si>
     <t>Name</t>
   </si>
@@ -203,21 +203,12 @@
     <t>La ruta del ejecutor de SAP Logon</t>
   </si>
   <si>
-    <t>MainTransaction</t>
-  </si>
-  <si>
     <t>AMP14_00_LiberarCalculoCoste</t>
   </si>
   <si>
     <t>saplogon.exe;EXCEL</t>
   </si>
   <si>
-    <t>SAP_LCCostesTransaction</t>
-  </si>
-  <si>
-    <t>Transacción principal para ejecutar en SAP robot AMP 14 Liberar Calculo Costes</t>
-  </si>
-  <si>
     <t>InitialInpuPath</t>
   </si>
   <si>
@@ -252,24 +243,47 @@
   </si>
   <si>
     <t>Nombres de disposicion en SAP</t>
+  </si>
+  <si>
+    <t>ODM_TimeoutShort</t>
+  </si>
+  <si>
+    <t>ODM_TimeoutMedium</t>
+  </si>
+  <si>
+    <t>ODM_TimeoutLong</t>
+  </si>
+  <si>
+    <t>Timeout corto para interactuar en ODM</t>
+  </si>
+  <si>
+    <t>Timeout medio para interactuar en ODM</t>
+  </si>
+  <si>
+    <t>Timeout largo para interactuar en ODM</t>
+  </si>
+  <si>
+    <t>ODM_URL</t>
+  </si>
+  <si>
+    <t>La URL para abrir la app de ODM</t>
+  </si>
+  <si>
+    <t>ODM_Creds</t>
+  </si>
+  <si>
+    <t>Crdenciales para logueo en ODM</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -358,14 +372,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -656,7 +669,7 @@
         <v>9</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>10</v>
@@ -667,7 +680,7 @@
         <v>54</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>55</v>
@@ -685,9 +698,15 @@
       </c>
     </row>
     <row r="7" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
+      <c r="A7" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="9" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2858,7 +2877,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:Z983"/>
+  <dimension ref="A1:Z985"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="31.85546875" customWidth="1"/>
@@ -2960,78 +2979,117 @@
       </c>
     </row>
     <row r="6" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>61</v>
+      <c r="A6" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>72</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="9" t="s">
-        <v>62</v>
+      <c r="D6" s="3" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>68</v>
+        <v>73</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>73</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="10" t="s">
-        <v>64</v>
+      <c r="D7" s="3" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>69</v>
+        <v>74</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>74</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="10" t="s">
-        <v>66</v>
+      <c r="D8" s="3" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>67</v>
+      <c r="A9" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>65</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D9" s="11" t="s">
-        <v>70</v>
+      <c r="D9" s="8" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>72</v>
+      <c r="A10" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>66</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="11" t="s">
-        <v>74</v>
+      <c r="D10" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
-    <row r="11" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>79</v>
+      </c>
+    </row>
     <row r="14" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="15" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="16" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -3222,8 +3280,8 @@
     <row r="201" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="202" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="203" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="204" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="205" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -4002,6 +4060,8 @@
     <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape" r:id="rId1"/>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aci-cns\Documents\UiPath\AMP06_00_InformeSeguimientoRepuestos\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4D75E32-DB33-479D-93E4-D2F8217293B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAA59AAC-4A51-4A9C-802E-AED97E24755F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,8 +17,19 @@
     <sheet name="Constants" sheetId="2" r:id="rId2"/>
     <sheet name="Assets" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId7" roundtripDataChecksum="54QOzkJ5yUFRx/cu0Hfc+S94/d7KJAOULguWs82GEDY="/>
     </ext>
@@ -27,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="85">
   <si>
     <t>Name</t>
   </si>
@@ -215,21 +226,9 @@
     <t>Ruta del insumo inicial incluido el nombre del archivo</t>
   </si>
   <si>
-    <t>InputSheetName</t>
-  </si>
-  <si>
-    <t>Nombre de la hoja por procesar del insumo inicial</t>
-  </si>
-  <si>
     <t>ISR_SAPVariantes</t>
   </si>
   <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
     <t>Nombres de variantes en SAP</t>
   </si>
   <si>
@@ -273,6 +272,27 @@
   </si>
   <si>
     <t>Crdenciales para logueo en ODM</t>
+  </si>
+  <si>
+    <t>ISR_InitialInpuPath</t>
+  </si>
+  <si>
+    <t>FinalReportName</t>
+  </si>
+  <si>
+    <t>Nombre del reporte final</t>
+  </si>
+  <si>
+    <t>SEGUIMIENTO REPUESTOS {0}.xlsm</t>
+  </si>
+  <si>
+    <t>ISR_SAPBatchIntervals</t>
+  </si>
+  <si>
+    <t>SAPBatchIntervals</t>
+  </si>
+  <si>
+    <t>Intervalos de lotes para ingresarlos a las transacciones SAP, el guion separa el intervalo y el punto y coma separa el par</t>
   </si>
 </sst>
 </file>
@@ -698,17 +718,27 @@
       </c>
     </row>
     <row r="7" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="B7" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>81</v>
-      </c>
     </row>
-    <row r="8" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="9" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="10" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
@@ -2877,7 +2907,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:Z985"/>
+  <dimension ref="A1:Z984"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="31.85546875" customWidth="1"/>
@@ -2979,67 +3009,67 @@
       </c>
     </row>
     <row r="6" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>72</v>
+      <c r="A6" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>68</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>73</v>
+      <c r="A7" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>69</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>74</v>
+      <c r="A8" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>70</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="B9" s="9" t="s">
-        <v>65</v>
+      <c r="B9" s="10" t="s">
+        <v>78</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="10" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="B10" s="8" t="s">
         <v>62</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>66</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>7</v>
@@ -3049,45 +3079,45 @@
       </c>
     </row>
     <row r="11" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>64</v>
+      <c r="A11" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>65</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="D11" s="8" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="12" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -3281,7 +3311,7 @@
     <row r="202" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="203" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="204" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="205" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -4061,7 +4091,6 @@
     <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape" r:id="rId1"/>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aci-cns\Documents\UiPath\AMP06_00_InformeSeguimientoRepuestos\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAA59AAC-4A51-4A9C-802E-AED97E24755F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE2ABAED-82CB-4B48-8E14-07AFF696F78C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="94">
   <si>
     <t>Name</t>
   </si>
@@ -271,9 +271,6 @@
     <t>ODM_Creds</t>
   </si>
   <si>
-    <t>Crdenciales para logueo en ODM</t>
-  </si>
-  <si>
     <t>ISR_InitialInpuPath</t>
   </si>
   <si>
@@ -293,13 +290,43 @@
   </si>
   <si>
     <t>Intervalos de lotes para ingresarlos a las transacciones SAP, el guion separa el intervalo y el punto y coma separa el par</t>
+  </si>
+  <si>
+    <t>ISR_MacroName</t>
+  </si>
+  <si>
+    <t>MacroName</t>
+  </si>
+  <si>
+    <t>Nombre de la macro a ejecutar dentro del reporte Seguimiento Respuestos</t>
+  </si>
+  <si>
+    <t>Datos de Validación Compras</t>
+  </si>
+  <si>
+    <t>Credenciales para logueo en ODM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nombre de la hoja del reporte ODM </t>
+  </si>
+  <si>
+    <t>ODM_SheetName</t>
+  </si>
+  <si>
+    <t>Data</t>
+  </si>
+  <si>
+    <t>SAP_SheetName</t>
+  </si>
+  <si>
+    <t>Nombre de la hoja del reportes SAP</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -371,6 +398,13 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -392,7 +426,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -404,6 +438,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -619,7 +654,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z998"/>
+  <dimension ref="A1:Z997"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="43.5703125" customWidth="1"/>
@@ -718,30 +753,48 @@
       </c>
     </row>
     <row r="7" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>77</v>
+      <c r="C7" s="10" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="B8" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>80</v>
-      </c>
     </row>
-    <row r="9" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
     <row r="10" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="4"/>
+      <c r="A10" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="11" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="12" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -950,7 +1003,7 @@
     <row r="215" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="216" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="217" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="218" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1730,7 +1783,6 @@
     <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2910,143 +2962,144 @@
   <dimension ref="A1:Z984"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="31.85546875" customWidth="1"/>
-    <col min="2" max="2" width="30.140625" customWidth="1"/>
-    <col min="3" max="3" width="31" customWidth="1"/>
-    <col min="4" max="24" width="65.42578125" customWidth="1"/>
+    <col min="1" max="1" width="31.85546875" style="4" customWidth="1"/>
+    <col min="2" max="2" width="30.140625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="31" style="4" customWidth="1"/>
+    <col min="4" max="24" width="65.42578125" style="4" customWidth="1"/>
+    <col min="25" max="16384" width="14.42578125" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
-      <c r="T1" s="1"/>
-      <c r="U1" s="1"/>
-      <c r="V1" s="1"/>
-      <c r="W1" s="1"/>
-      <c r="X1" s="1"/>
-      <c r="Y1" s="1"/>
-      <c r="Z1" s="1"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
+      <c r="L1" s="11"/>
+      <c r="M1" s="11"/>
+      <c r="N1" s="11"/>
+      <c r="O1" s="11"/>
+      <c r="P1" s="11"/>
+      <c r="Q1" s="11"/>
+      <c r="R1" s="11"/>
+      <c r="S1" s="11"/>
+      <c r="T1" s="11"/>
+      <c r="U1" s="11"/>
+      <c r="V1" s="11"/>
+      <c r="W1" s="11"/>
+      <c r="X1" s="11"/>
+      <c r="Y1" s="11"/>
+      <c r="Z1" s="11"/>
     </row>
     <row r="2" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="10" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="10" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="10" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="10" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="10" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="10" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
+      <c r="A8" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="10" t="s">
         <v>73</v>
       </c>
     </row>
@@ -3055,9 +3108,9 @@
         <v>60</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="C9" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C9" s="10" t="s">
         <v>7</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -3065,1032 +3118,1045 @@
       </c>
     </row>
     <row r="10" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="10" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="10" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="12" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="9" t="s">
+      <c r="A12" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="D12" s="10" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="B13" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="C13" s="3" t="s">
+    </row>
+    <row r="14" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="C14" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D13" s="10" t="s">
-        <v>84</v>
+      <c r="D14" s="10" t="s">
+        <v>86</v>
       </c>
     </row>
-    <row r="14" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="15" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="16" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="18" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="19" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="20" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="22" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="27" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="28" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="33" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="34" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="36" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="37" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="38" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="39" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="40" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="41" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="42" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="43" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="44" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="47" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="48" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="49" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="50" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="51" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="52" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="53" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="54" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="55" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="56" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="57" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="58" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="64" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="65" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="66" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="67" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="68" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="69" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="70" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="71" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="72" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="73" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="75" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="76" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="77" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="79" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="80" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="81" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="82" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="83" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="87" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="88" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="90" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="91" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="92" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="93" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="94" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="95" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="96" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="97" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="98" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="99" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="100" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="101" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="102" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="103" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="104" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="105" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="106" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="107" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="108" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="109" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="110" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="111" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="112" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="113" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="114" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="115" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="116" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="117" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="118" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="119" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="120" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="121" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="122" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="123" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="124" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="125" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="126" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="127" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="128" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="129" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="130" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="131" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="132" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="133" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="134" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="135" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="136" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="137" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="138" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="139" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="140" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="141" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="142" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="143" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="144" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="145" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="146" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="147" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="148" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="149" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="150" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="151" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="152" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="153" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="154" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="155" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="156" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="157" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="158" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="159" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="160" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="161" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="162" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="163" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="164" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="165" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="166" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="167" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="168" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="169" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="170" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="171" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="172" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="173" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="174" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="175" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="176" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="177" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="178" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="179" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="180" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="181" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="182" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="183" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="184" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="185" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="186" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="187" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="188" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="189" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="190" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="191" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="192" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="193" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="194" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="195" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="196" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="197" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="198" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="199" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="200" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="201" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="202" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="203" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="204" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="18" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="19" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="20" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="118" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="119" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="125" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="166" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="167" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="168" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="169" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="170" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="171" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="172" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="173" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="174" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="175" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="176" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="177" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="178" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="179" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="180" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="181" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="182" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="183" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="184" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="185" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="186" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="187" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="188" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="189" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="190" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="191" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="192" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="193" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="194" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="195" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="196" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="197" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="198" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="199" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="200" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="201" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="202" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="203" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="204" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="205" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="206" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="207" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="208" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="209" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="210" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="211" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="212" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="213" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="214" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="215" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="216" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="217" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="218" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="219" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="220" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="221" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="222" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="223" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="224" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="225" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="226" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="227" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="228" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="229" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="230" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="231" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="232" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="233" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="234" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="235" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="236" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="237" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="238" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="239" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="240" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="241" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="242" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="243" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="244" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="245" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="246" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="247" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="248" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="249" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="250" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="251" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="252" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="253" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="254" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="255" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="256" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="257" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="258" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="259" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="260" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="261" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="262" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="263" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="264" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="265" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="266" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="267" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="268" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="269" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="270" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="271" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="272" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="273" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="274" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="275" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="276" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="277" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="278" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="279" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="280" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="281" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="282" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="283" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="284" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="285" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="286" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="287" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="288" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="289" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="290" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="291" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="292" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="293" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="294" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="295" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="296" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="297" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="298" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="299" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="300" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="301" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="302" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="303" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="304" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="305" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="306" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="307" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="308" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="309" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="310" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="311" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="312" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="313" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="314" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="315" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="316" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="317" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="318" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="319" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="320" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="321" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="322" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="323" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="324" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="325" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="326" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="327" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="328" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="329" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="330" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="331" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="332" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="333" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="334" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="335" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="336" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="337" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="338" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="339" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="340" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="341" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="342" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="343" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="344" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="345" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="346" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="347" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="348" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="349" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="350" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="351" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="352" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="353" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="354" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="355" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="356" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="357" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="358" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="359" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="360" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="361" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="362" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="363" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="364" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="365" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="366" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="367" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="368" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="369" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="370" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="371" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="372" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="373" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="374" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="375" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="376" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="377" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="378" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="379" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="380" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="381" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="382" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="383" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="384" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="385" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="386" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="387" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="388" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="389" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="390" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="391" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="392" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="393" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="394" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="395" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="396" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="397" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="398" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="399" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="400" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="401" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="402" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="403" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="404" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="405" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="406" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="407" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="408" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="409" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="410" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="411" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="412" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="413" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="414" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="415" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="416" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="417" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="418" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="419" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="420" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="421" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="422" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="423" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="424" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="425" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="426" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="427" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="428" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="429" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="430" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="431" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="432" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="433" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="434" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="435" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="436" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="437" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="438" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="439" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="440" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="441" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="442" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="443" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="444" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="445" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="446" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="447" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="448" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="449" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="450" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="451" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="452" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="453" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="454" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="455" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="456" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="457" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="458" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="459" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="460" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="461" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="462" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="463" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="464" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="465" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="466" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="467" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="468" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="469" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="470" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="471" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="472" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="473" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="474" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="475" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="476" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="477" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="478" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="479" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="480" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="481" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="482" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="483" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="484" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="485" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="486" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="487" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="488" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="489" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="490" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="491" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="492" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="493" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="494" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="495" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="496" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="497" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="498" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="499" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="500" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="501" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="502" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="503" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="504" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="505" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="506" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="507" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="508" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="509" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="510" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="511" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="512" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="513" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="514" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="515" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="516" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="517" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="518" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="519" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="520" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="521" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="522" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="523" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="524" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="525" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="526" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="527" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="528" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="529" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="530" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="531" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="532" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="533" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="534" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="535" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="536" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="537" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="538" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="539" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="540" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="541" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="542" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="543" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="544" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="545" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="546" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="547" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="548" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="549" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="550" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="551" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="552" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="553" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="554" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="555" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="556" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="557" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="558" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="559" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="560" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="561" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="562" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="563" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="564" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="565" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="566" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="567" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="568" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="569" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="570" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="571" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="572" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="573" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="574" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="575" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="576" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="577" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="578" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="579" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="580" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="581" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="582" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="583" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="584" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="585" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="586" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="587" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="588" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="589" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="590" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="591" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="592" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="593" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="594" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="595" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="596" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="597" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="598" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="599" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="600" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="601" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="602" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="603" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="604" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="605" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="606" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="607" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="608" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="609" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="610" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="611" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="612" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="613" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="614" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="615" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="616" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="617" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="618" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="619" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="620" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="621" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="622" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="623" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="624" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="625" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="626" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="627" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="628" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="629" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="630" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="631" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="632" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="633" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="634" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="635" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="636" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="637" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="638" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="639" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="640" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="641" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="642" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="643" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="644" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="645" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="646" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="647" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="648" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="649" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="650" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="651" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="652" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="653" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="654" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="655" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="656" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="657" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="658" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="659" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="660" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="661" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="662" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="663" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="664" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="665" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="666" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="667" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="668" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="669" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="670" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="671" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="672" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="673" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="674" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="675" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="676" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="677" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="678" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="679" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="680" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="681" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="682" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="683" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="684" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="685" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="686" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="687" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="688" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="689" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="690" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="691" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="692" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="693" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="694" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="695" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="696" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="697" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="698" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="699" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="700" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="701" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="702" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="703" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="704" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="705" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="706" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="707" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="708" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="709" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="710" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="711" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="712" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="713" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="714" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="715" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="716" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="717" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="718" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="719" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="720" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="721" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="722" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="723" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="724" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="725" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="726" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="727" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="728" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="729" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="730" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="731" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="732" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="733" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="734" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="735" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="736" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="737" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="738" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="739" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="740" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="741" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="742" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="743" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="744" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="745" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="746" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="747" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="748" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="749" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="750" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="751" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="752" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="753" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="754" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="755" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="756" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="757" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="758" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="759" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="760" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="761" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="762" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="763" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="764" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="765" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="766" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="767" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="768" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="769" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="770" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="771" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="772" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="773" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="774" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="775" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="776" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="777" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="778" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="779" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="780" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="781" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="782" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="783" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="784" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="785" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="786" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="787" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="788" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="789" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="790" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="791" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="792" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="793" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="794" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="795" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="796" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="797" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="798" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="799" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="800" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="801" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="802" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="803" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="804" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="805" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="806" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="807" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="808" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="809" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="810" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="811" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="812" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="813" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="814" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="815" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="816" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="817" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="818" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="819" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="820" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="821" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="822" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="823" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="824" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="825" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="826" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="827" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="828" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="829" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="830" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="831" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="832" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="833" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="834" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="835" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="836" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="837" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="838" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="839" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="840" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="841" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="842" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="843" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="844" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="845" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="846" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="847" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="848" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="849" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="850" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="851" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="852" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="853" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="854" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="855" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="856" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="857" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="858" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="859" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="860" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="861" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="862" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="863" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="864" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="865" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="866" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="867" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="868" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="869" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="870" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="871" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="872" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="873" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="874" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="875" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="876" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="877" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="878" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="879" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="880" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="881" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="882" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="883" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="884" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="885" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="886" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="887" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="888" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="889" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="890" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="891" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="892" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="893" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="894" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="895" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="896" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="897" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="898" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="899" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="900" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="901" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="902" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="903" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="904" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="905" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="906" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="907" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="908" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="909" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="910" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="911" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="912" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="913" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="914" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="915" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="916" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="917" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="918" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="919" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="920" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="921" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="922" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="923" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="924" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="925" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="926" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="927" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="928" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="929" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="930" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="931" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="932" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="933" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="934" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="935" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="936" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="937" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="938" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="939" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="940" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="941" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="942" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="943" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="944" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="945" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="946" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="947" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="948" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="949" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="950" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="951" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="952" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="953" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="954" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="955" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="956" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="957" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="958" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="959" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="960" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="961" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="962" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="963" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="964" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="965" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="966" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="967" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="968" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="969" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="970" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="971" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="972" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="973" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="974" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="975" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="976" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="977" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="978" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="979" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="980" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="981" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="982" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="983" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="984" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape" r:id="rId1"/>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aci-cns\Documents\UiPath\AMP06_00_InformeSeguimientoRepuestos\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE2ABAED-82CB-4B48-8E14-07AFF696F78C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE428DF9-8C4C-4789-B977-4054707ED325}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -214,12 +214,6 @@
     <t>La ruta del ejecutor de SAP Logon</t>
   </si>
   <si>
-    <t>AMP14_00_LiberarCalculoCoste</t>
-  </si>
-  <si>
-    <t>saplogon.exe;EXCEL</t>
-  </si>
-  <si>
     <t>InitialInpuPath</t>
   </si>
   <si>
@@ -320,17 +314,30 @@
   </si>
   <si>
     <t>Nombre de la hoja del reportes SAP</t>
+  </si>
+  <si>
+    <t>AMP06_00_InformeSeguimientoRepuestos</t>
+  </si>
+  <si>
+    <t>saplogon.exe;EXCEL;msedge.exe</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -426,19 +433,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -724,7 +732,7 @@
         <v>9</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>10</v>
@@ -735,7 +743,7 @@
         <v>54</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>59</v>
+        <v>93</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>55</v>
@@ -754,49 +762,51 @@
     </row>
     <row r="7" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="B8" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="B8" s="9" t="s">
-        <v>80</v>
-      </c>
       <c r="C8" s="5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B9" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>87</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B10" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="C10" s="5" t="s">
-        <v>93</v>
-      </c>
     </row>
-    <row r="11" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="4"/>
+    </row>
     <row r="12" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="13" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -3063,128 +3073,128 @@
     </row>
     <row r="6" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>68</v>
+        <v>66</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>66</v>
       </c>
       <c r="C6" s="10" t="s">
         <v>7</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>69</v>
+        <v>67</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>67</v>
       </c>
       <c r="C7" s="10" t="s">
         <v>7</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>70</v>
+        <v>68</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>68</v>
       </c>
       <c r="C8" s="10" t="s">
         <v>7</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>77</v>
+        <v>58</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>75</v>
       </c>
       <c r="C9" s="10" t="s">
         <v>7</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="B10" s="10" t="s">
         <v>62</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>60</v>
       </c>
       <c r="C10" s="10" t="s">
         <v>7</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>65</v>
+        <v>64</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>63</v>
       </c>
       <c r="C11" s="10" t="s">
         <v>7</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>74</v>
+        <v>72</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>72</v>
       </c>
       <c r="C12" s="10" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>79</v>
       </c>
       <c r="C13" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D13" s="10" t="s">
-        <v>83</v>
+      <c r="D13" s="12" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="14" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>82</v>
       </c>
       <c r="C14" s="10" t="s">
         <v>7</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aci-cns\Documents\UiPath\AMP06_00_InformeSeguimientoRepuestos\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE428DF9-8C4C-4789-B977-4054707ED325}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66BFDEAE-1B2F-4871-B7CD-7E81F53D389A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="100">
   <si>
     <t>Name</t>
   </si>
@@ -320,17 +320,49 @@
   </si>
   <si>
     <t>saplogon.exe;EXCEL;msedge.exe</t>
+  </si>
+  <si>
+    <t>ISR_FinalFolderReportPath</t>
+  </si>
+  <si>
+    <t>Ruta de la carpeta para guardar el reporte final</t>
+  </si>
+  <si>
+    <t>FinalFolderReportPath</t>
+  </si>
+  <si>
+    <t>Intervalo de lotes transacción</t>
+  </si>
+  <si>
+    <t>BatchTransactionZSD053</t>
+  </si>
+  <si>
+    <t>35000000;35999999</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -433,19 +465,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -805,7 +839,15 @@
       </c>
     </row>
     <row r="11" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="4"/>
+      <c r="A11" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="12" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="13" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2969,7 +3011,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:Z984"/>
+  <dimension ref="A1:Z985"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="31.85546875" style="4" customWidth="1"/>
@@ -3117,7 +3159,7 @@
       <c r="A9" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="13" t="s">
         <v>75</v>
       </c>
       <c r="C9" s="10" t="s">
@@ -3128,1045 +3170,1059 @@
       </c>
     </row>
     <row r="10" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>60</v>
+      <c r="A10" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>94</v>
       </c>
       <c r="C10" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="10" t="s">
-        <v>61</v>
+      <c r="D10" s="13" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="11" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C11" s="10" t="s">
         <v>7</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="C12" s="10" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C13" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D13" s="12" t="s">
-        <v>81</v>
+      <c r="D13" s="10" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="14" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C14" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="D14" s="12" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="10" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="15" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="16" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="18" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="19" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="20" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="21" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="22" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="23" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="24" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="26" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="27" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="28" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="33" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="34" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="35" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="36" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="37" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="38" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="39" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="40" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="41" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="42" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="43" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="44" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="46" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="47" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="48" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="49" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="50" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="51" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="52" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="53" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="54" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="55" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="56" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="57" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="58" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="64" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="65" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="66" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="67" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="68" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="69" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="70" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="71" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="72" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="73" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="75" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="76" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="77" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="79" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="80" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="81" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="82" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="83" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="87" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="88" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="90" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="91" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="92" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="93" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="94" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="95" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="96" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="97" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="98" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="99" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="100" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="101" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="102" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="103" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="104" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="105" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="106" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="107" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="108" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="109" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="110" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="111" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="112" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="113" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="114" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="115" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="116" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="117" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="118" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="119" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="120" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="121" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="122" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="123" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="124" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="125" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="126" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="127" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="128" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="129" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="130" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="131" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="132" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="133" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="134" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="135" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="136" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="137" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="138" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="139" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="140" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="141" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="142" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="143" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="144" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="145" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="146" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="147" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="148" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="149" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="150" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="151" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="152" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="153" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="154" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="155" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="156" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="157" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="158" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="159" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="160" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="161" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="162" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="163" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="164" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="165" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="166" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="167" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="168" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="169" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="170" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="171" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="172" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="173" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="174" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="175" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="176" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="177" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="178" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="179" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="180" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="181" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="182" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="183" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="184" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="185" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="186" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="187" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="188" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="189" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="190" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="191" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="192" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="193" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="194" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="195" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="196" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="197" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="198" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="199" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="200" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="201" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="202" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="203" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="204" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="205" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="206" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="207" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="208" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="209" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="210" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="211" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="212" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="213" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="214" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="215" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="216" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="217" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="218" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="219" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="220" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="221" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="222" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="223" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="224" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="225" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="226" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="227" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="228" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="229" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="230" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="231" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="232" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="233" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="234" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="235" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="236" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="237" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="238" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="239" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="240" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="241" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="242" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="243" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="244" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="245" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="246" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="247" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="248" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="249" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="250" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="251" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="252" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="253" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="254" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="255" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="256" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="257" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="258" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="259" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="260" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="261" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="262" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="263" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="264" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="265" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="266" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="267" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="268" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="269" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="270" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="271" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="272" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="273" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="274" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="275" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="276" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="277" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="278" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="279" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="280" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="281" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="282" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="283" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="284" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="285" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="286" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="287" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="288" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="289" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="290" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="291" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="292" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="293" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="294" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="295" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="296" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="297" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="298" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="299" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="300" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="301" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="302" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="303" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="304" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="305" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="306" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="307" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="308" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="309" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="310" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="311" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="312" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="313" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="314" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="315" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="316" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="317" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="318" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="319" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="320" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="321" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="322" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="323" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="324" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="325" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="326" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="327" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="328" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="329" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="330" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="331" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="332" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="333" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="334" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="335" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="336" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="337" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="338" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="339" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="340" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="341" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="342" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="343" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="344" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="345" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="346" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="347" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="348" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="349" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="350" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="351" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="352" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="353" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="354" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="355" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="356" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="357" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="358" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="359" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="360" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="361" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="362" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="363" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="364" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="365" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="366" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="367" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="368" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="369" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="370" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="371" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="372" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="373" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="374" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="375" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="376" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="377" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="378" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="379" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="380" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="381" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="382" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="383" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="384" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="385" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="386" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="387" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="388" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="389" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="390" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="391" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="392" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="393" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="394" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="395" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="396" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="397" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="398" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="399" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="400" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="401" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="402" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="403" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="404" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="405" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="406" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="407" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="408" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="409" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="410" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="411" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="412" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="413" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="414" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="415" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="416" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="417" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="418" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="419" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="420" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="421" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="422" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="423" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="424" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="425" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="426" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="427" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="428" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="429" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="430" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="431" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="432" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="433" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="434" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="435" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="436" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="437" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="438" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="439" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="440" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="441" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="442" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="443" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="444" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="445" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="446" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="447" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="448" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="449" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="450" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="451" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="452" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="453" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="454" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="455" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="456" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="457" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="458" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="459" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="460" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="461" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="462" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="463" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="464" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="465" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="466" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="467" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="468" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="469" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="470" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="471" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="472" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="473" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="474" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="475" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="476" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="477" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="478" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="479" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="480" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="481" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="482" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="483" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="484" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="485" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="486" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="487" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="488" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="489" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="490" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="491" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="492" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="493" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="494" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="495" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="496" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="497" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="498" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="499" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="500" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="501" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="502" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="503" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="504" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="505" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="506" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="507" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="508" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="509" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="510" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="511" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="512" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="513" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="514" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="515" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="516" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="517" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="518" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="519" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="520" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="521" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="522" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="523" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="524" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="525" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="526" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="527" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="528" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="529" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="530" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="531" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="532" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="533" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="534" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="535" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="536" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="537" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="538" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="539" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="540" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="541" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="542" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="543" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="544" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="545" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="546" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="547" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="548" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="549" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="550" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="551" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="552" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="553" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="554" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="555" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="556" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="557" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="558" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="559" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="560" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="561" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="562" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="563" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="564" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="565" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="566" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="567" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="568" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="569" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="570" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="571" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="572" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="573" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="574" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="575" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="576" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="577" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="578" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="579" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="580" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="581" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="582" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="583" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="584" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="585" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="586" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="587" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="588" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="589" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="590" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="591" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="592" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="593" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="594" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="595" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="596" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="597" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="598" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="599" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="600" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="601" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="602" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="603" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="604" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="605" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="606" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="607" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="608" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="609" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="610" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="611" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="612" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="613" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="614" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="615" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="616" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="617" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="618" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="619" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="620" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="621" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="622" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="623" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="624" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="625" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="626" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="627" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="628" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="629" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="630" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="631" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="632" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="633" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="634" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="635" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="636" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="637" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="638" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="639" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="640" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="641" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="642" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="643" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="644" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="645" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="646" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="647" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="648" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="649" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="650" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="651" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="652" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="653" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="654" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="655" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="656" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="657" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="658" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="659" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="660" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="661" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="662" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="663" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="664" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="665" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="666" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="667" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="668" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="669" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="670" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="671" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="672" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="673" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="674" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="675" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="676" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="677" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="678" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="679" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="680" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="681" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="682" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="683" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="684" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="685" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="686" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="687" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="688" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="689" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="690" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="691" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="692" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="693" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="694" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="695" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="696" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="697" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="698" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="699" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="700" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="701" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="702" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="703" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="704" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="705" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="706" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="707" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="708" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="709" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="710" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="711" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="712" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="713" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="714" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="715" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="716" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="717" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="718" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="719" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="720" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="721" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="722" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="723" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="724" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="725" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="726" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="727" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="728" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="729" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="730" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="731" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="732" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="733" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="734" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="735" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="736" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="737" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="738" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="739" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="740" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="741" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="742" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="743" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="744" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="745" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="746" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="747" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="748" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="749" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="750" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="751" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="752" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="753" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="754" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="755" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="756" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="757" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="758" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="759" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="760" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="761" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="762" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="763" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="764" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="765" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="766" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="767" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="768" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="769" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="770" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="771" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="772" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="773" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="774" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="775" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="776" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="777" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="778" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="779" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="780" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="781" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="782" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="783" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="784" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="785" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="786" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="787" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="788" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="789" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="790" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="791" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="792" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="793" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="794" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="795" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="796" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="797" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="798" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="799" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="800" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="801" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="802" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="803" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="804" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="805" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="806" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="807" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="808" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="809" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="810" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="811" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="812" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="813" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="814" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="815" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="816" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="817" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="818" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="819" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="820" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="821" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="822" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="823" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="824" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="825" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="826" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="827" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="828" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="829" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="830" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="831" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="832" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="833" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="834" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="835" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="836" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="837" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="838" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="839" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="840" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="841" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="842" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="843" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="844" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="845" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="846" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="847" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="848" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="849" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="850" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="851" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="852" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="853" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="854" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="855" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="856" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="857" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="858" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="859" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="860" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="861" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="862" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="863" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="864" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="865" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="866" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="867" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="868" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="869" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="870" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="871" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="872" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="873" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="874" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="875" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="876" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="877" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="878" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="879" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="880" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="881" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="882" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="883" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="884" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="885" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="886" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="887" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="888" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="889" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="890" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="891" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="892" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="893" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="894" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="895" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="896" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="897" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="898" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="899" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="900" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="901" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="902" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="903" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="904" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="905" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="906" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="907" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="908" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="909" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="910" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="911" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="912" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="913" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="914" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="915" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="916" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="917" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="918" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="919" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="920" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="921" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="922" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="923" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="924" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="925" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="926" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="927" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="928" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="929" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="930" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="931" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="932" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="933" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="934" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="935" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="936" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="937" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="938" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="939" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="940" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="941" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="942" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="943" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="944" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="945" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="946" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="947" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="948" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="949" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="950" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="951" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="952" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="953" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="954" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="955" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="956" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="957" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="958" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="959" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="960" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="961" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="962" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="963" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="964" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="965" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="966" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="967" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="968" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="969" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="970" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="971" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="972" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="973" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="974" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="975" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="976" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="977" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="978" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="979" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="980" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="981" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="982" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="983" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="984" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="18" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="19" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="20" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="118" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="119" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="125" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="166" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="167" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="168" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="169" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="170" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="171" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="172" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="173" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="174" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="175" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="176" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="177" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="178" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="179" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="180" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="181" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="182" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="183" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="184" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="185" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="186" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="187" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="188" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="189" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="190" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="191" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="192" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="193" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="194" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="195" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="196" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="197" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="198" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="199" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="200" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="201" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="202" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="203" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="204" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="205" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape" r:id="rId1"/>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aci-cns\Documents\UiPath\AMP06_00_InformeSeguimientoRepuestos\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66BFDEAE-1B2F-4871-B7CD-7E81F53D389A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F7B8068-2064-4229-A1DD-F7F245E67DCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="102">
   <si>
     <t>Name</t>
   </si>
@@ -338,17 +338,30 @@
   </si>
   <si>
     <t>35000000;35999999</t>
+  </si>
+  <si>
+    <t>ODM_MenuName</t>
+  </si>
+  <si>
+    <t>Nombre del menú en ODM</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -465,19 +478,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3253,7 +3267,20 @@
         <v>84</v>
       </c>
     </row>
-    <row r="16" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="15" t="s">
+        <v>101</v>
+      </c>
+    </row>
     <row r="17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="18" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="19" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aci-cns\Documents\UiPath\AMP06_00_InformeSeguimientoRepuestos\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F7B8068-2064-4229-A1DD-F7F245E67DCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2075072A-2960-4209-9F00-FA52B58C4930}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="108">
   <si>
     <t>Name</t>
   </si>
@@ -344,17 +344,52 @@
   </si>
   <si>
     <t>Nombre del menú en ODM</t>
+  </si>
+  <si>
+    <t>RangeData</t>
+  </si>
+  <si>
+    <t>Transaction;Range
+ZMG002_01;B2
+ZMM026;C2
+LX02;E2
+COHV;C2
+ZCO017;B2
+ZPP029_1;A2
+MB52;C2
+ZSD053;C2
+LT23;C2
+VL06O;A2</t>
+  </si>
+  <si>
+    <t>DefaultRange</t>
+  </si>
+  <si>
+    <t>B2</t>
+  </si>
+  <si>
+    <t>Los rangos para cada una de las transacciones</t>
+  </si>
+  <si>
+    <t>El rango por defecto</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -478,23 +513,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -863,8 +902,28 @@
         <v>97</v>
       </c>
     </row>
-    <row r="12" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="B12" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>107</v>
+      </c>
+    </row>
     <row r="14" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="15" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="16" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
